--- a/Osv60_soc_taxi_2025.xlsx
+++ b/Osv60_soc_taxi_2025.xlsx
@@ -683,7 +683,7 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>57911.1</v>
+        <v>46774.35</v>
       </c>
     </row>
     <row r="6">
@@ -730,7 +730,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>65824.2</v>
+        <v>53165.7</v>
       </c>
     </row>
     <row r="7">
@@ -1059,7 +1059,7 @@
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>4830.2826</v>
+        <v>3901.3821</v>
       </c>
     </row>
     <row r="14">
@@ -1153,7 +1153,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>7784.400000000001</v>
+        <v>6287.4</v>
       </c>
     </row>
     <row r="16">
@@ -1200,7 +1200,7 @@
         <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>44649.9066</v>
+        <v>36063.3861</v>
       </c>
     </row>
     <row r="17">
@@ -1294,7 +1294,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>51072.2862</v>
+        <v>41250.6927</v>
       </c>
     </row>
     <row r="19">
@@ -1341,7 +1341,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>7796.1</v>
+        <v>6296.85</v>
       </c>
     </row>
     <row r="20">
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>114621</v>
+        <v>92578.5</v>
       </c>
     </row>
   </sheetData>
@@ -1505,7 +1505,7 @@
         <v>269670.76</v>
       </c>
       <c r="C4" t="n">
-        <v>210343.1928</v>
+        <v>169892.5788</v>
       </c>
     </row>
     <row r="5">
@@ -1544,7 +1544,7 @@
         <v>0</v>
       </c>
       <c r="C7" t="n">
-        <v>7784.400000000001</v>
+        <v>6287.4</v>
       </c>
     </row>
     <row r="8">
@@ -1570,7 +1570,7 @@
         <v>158635</v>
       </c>
       <c r="C9" t="n">
-        <v>136361.6826</v>
+        <v>110138.2821</v>
       </c>
     </row>
     <row r="10">
@@ -1888,7 +1888,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>354489.2754</v>
+        <v>286318.2609</v>
       </c>
     </row>
     <row r="9">
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3969526.4954</v>
+        <v>3901355.4809</v>
       </c>
     </row>
   </sheetData>
